--- a/Ground_test.xlsx
+++ b/Ground_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Reasearch-Intelligence-agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522FBCCB-39CB-4AFB-AE4A-BF8AE8B5745B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C8F515-D9D7-4EC6-8AD7-525CA17AB6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Query_id</t>
   </si>
@@ -172,6 +172,35 @@
       </rPr>
       <t xml:space="preserve"> This entity and event are entirely fictitious. The search tool must find no valid peer-reviewed material, and the pipeline must trigger its safe fallback mechanism.</t>
     </r>
+  </si>
+  <si>
+    <t>Answers</t>
+  </si>
+  <si>
+    <t>InvalidQueryError(
+  'The topic or keyword in this query does not appear to exist. Search was not performed.'
+)</t>
+  </si>
+  <si>
+    <t>{"output":"Based on the provided context, the most recent milestones in quantum computing error correction include the demonstration of dynamic surface codes on Google's Willow processor, the validation of high-rate LDPC codes by IBM Quantum, and the development of the dual-rail cat code by Chalmers University.\n\n*   **Dynamic Surface Codes (Google):** Researchers demonstrated that as the code distance scales from 3 to 5, the logical error rate improves by a factor of **2.15**, matching the performance of traditional static circuits. This work validates the viability of error correction beyond static models and aims for a logical qubit with an error rate of **less than one error per million cycles** (Source: research.google).\n*   **High-Rate LDPC Codes (IBM Quantum):** IBM presented Bivariate Bicycle (BB) codes that achieve an error threshold of **0.8%**, which is on par with the surface code. These codes provide a **more than 10× reduction in physical qubits** needed for comparable error suppression (Source: alphaxiv.org).\n*   **Dual-Rail Cat Code (Chalmers University):** A new concatenated bosonic encoding scheme was introduced that achieves a **five-fold improvement** in quantum error correction capability, progressing from correcting single erasure errors to addressing up to **d-1 errors** with a distance-d code (Source: quantumzeitgeist.com).\n*   **Phantom Codes (Harvard):** A class of codes was introduced that realizes logical entangling gates via qubit relabelling, achieving a circuit-noise threshold exceeding **0.5%** and logical error rates below **6×10⁻¹⁰** with modest post-selection (Source: lukin.physics.harvard.edu).\n\nNote: While the context mentions a \"2.14-fold reduction\" for the Surface Code on Willow (Source: qblox.com), the specific Google research blog cites a \"2.15\" factor for the dynamic code scaling from distance 3 to 5. The context does not provide specific publication dates for these milestones, so their placement within the last 12 months cannot be strictly verified from the text alone, though they are presented as recent achievements.\n\nSources:\n*   https://research.google/blog/dynamic-surface-codes-open-new-avenues-for-quantum-error-correction\n*   https://www.alphaxiv.org/abs/2308.07915\n*   https://quantumzeitgeist.com/quantum-error-correction-bosonic-codes-photon-loss-handling\n*   https://lukin.physics.harvard.edu/QEC-overhead\n*   https://qblox.com/newsroom/the-quantum-leap-that-needs-error-correction"}</t>
+  </si>
+  <si>
+    <t>{"output":"The most significant recent breakthrough is the achievement of a superconducting transition temperature (Tc) of **151 Kelvin** at ambient pressure by University of Houston researchers, which surpasses the previous record of **133 K**. This milestone was accomplished using a technique called pressure quenching, which preserves enhanced superconducting properties after pressure is removed. While room-temperature superconductivity (approx. 300 K) remains out of reach, this new record narrows the gap to about 140 degrees Celsius.\n\nSupporting details from recent 2025–2026 publications and preprints include:\n\n*   **151 K Record (2026):** University of Houston scientists from the Texas Center for Superconductivity (TcSUH) reported a Tc of **151 K** (approx. -122°C) at ambient pressure, the highest ever reported for a superconductor functioning at ambient pressure since 1911 (Source: sciencedaily.com, phys.org).\n*   **130 K+ Preprints (2025):** A 2025 preprint reported high-Tc superconductivity above **130 K** in cubic MH4 compounds at ambient pressure (Source: addi.ehu.es).\n*   **Theoretical Predictions (2026):** A study published in *npj Computational Materials* in March 2026 predicted ambient-pressure high-temperature superconductivity in electronically modified transition-metal hydrides (Source: nature.com).\n*   **Hydride Context:** Previous high-Tc records in hydrides required extreme pressures, such as **250 K** in lanthanum hydride at high pressure (2019) and **260 K** in lanthanum superhydride (2019), highlighting the significance of the new ambient-pressure achievement (Source: addi.ehu.es).\n\nSources:\n*   https://www.sciencedaily.com/releases/2026/05/260527023220.htm\n*   https://phys.org/news/2026-03-ceramic-shatters-longstanding-high-temperature.html\n*   https://addi.ehu.es/bitstream/handle/10810/78673/2026_CommPhys_Sanna_Search%20for%20thermodynamically%20stable%20ambient-pressure%20superconducting%20hydrides%20in%20the%20GNoME%20database.pdf?sequence=1\n*   https://www.nature.com/articles/s41524-026-02040-x\n*   https://www.pnas.org/doi/pdf/10.1073/pnas.2520324123"}</t>
+  </si>
+  <si>
+    <t>{"output":"Based on the provided context, the key architectural changes in recent state-of-the-art LLMs focus on **Multi-Head Latent Attention (MLA)** and **Multi-Token Prediction (MTP)** to optimize inference efficiency and generation speed.\n\n**Key Architectural Changes:**\n\n*   **Multi-Head Latent Attention (MLA):** This mechanism compresses key and value tensors into a lower-dimensional latent space before storing them in the KV cache, rather than sharing heads as in Grouped Query Attention (GQA). This approach achieves a **75.19% reduction** in total KV cache memory usage compared to standard Multi-Head Attention (MHA) (specifically reducing from **3.25 GB** to **0.81 GB** in cited examples) while slightly outperforming MHA in modeling performance. MLA is utilized in models such as DeepSeek V2, V3, and R1 (Source: github.com/rasbt/LLMs-from-scratch, linkedin.com).\n*   **Multi-Token Prediction (MTP):** This paradigm modifies the transformer backbone to predict **n future tokens simultaneously** at each position, rather than minimizing cross-entropy loss for only the immediate next token. This approach allows the model to \"look ahead,\" yielding significantly stronger performance and enabling inference engines to generate tokens **3x faster** and cheaper by predicting multiple future tokens instead of one at a time (Source: towardsdatascience.com, levelup.gitconnected.com).\n*   **Multi-Head Temporal Latent Attention (MTLA):** A newer proposed mechanism that temporally compresses the KV cache. MTLA matches MHA and MLA in accuracy while greatly increasing processing speed and reducing GPU memory usage during inference, requiring no changes beyond the attention module itself (Source: arxiv.org).\n\n**Note on \"Newest\" Models:**\nThe context does not explicitly list specific model names released \"this year\" (2026) other than referencing DeepSeek V2/V3/R1 for MLA and general modern LLMs (Llama 2-4, GPT-OSS, Gemma 3, Qwen 3, GLM 4.6) for standard attention variants. The specific architectural innovations described (MLA, MTP, MTLA) are the primary technical shifts highlighted in the provided sources.\n\nSources:\n*   https://arxiv.org/pdf/2505.13544\n*   https://github.com/rasbt/LLMs-from-scratch/blob/main/ch04/05_mla/README.md\n*   https://towardsdatascience.com/why-weve-been-optimizing-the-wrong-thing-in-llms-for-years\n*   https://www.linkedin.com/posts/sebastianraschka_multi-head-attention-mha-is-the-engine-activity-7383510781717487616-p11e\n*   https://levelup.gitconnected.com/mtp-and-dflash-how-llms-generate-tokens-3x-faster-and-cheaper-e3a09535c7a0"}</t>
+  </si>
+  <si>
+    <t>{"output":"The primary efficiency limitations in perovskite-silicon tandem solar cells are **interfacial non-radiative recombination** at the perovskite/electron transport layer (ETL) interface, **optical losses** from reflection and parasitic absorption, and **degradation-induced series resistance** caused by ionic migration and mechanical stress.\n\n*   **Interfacial Recombination Losses:** Non-radiative recombination at the perovskite/ETL interface is a critical barrier to high performance. Bilayer passivation strategies have been shown to reduce transport loss to as low as **5.1%** (in PVSK/AlOx/PDAI2 samples), compared to **6.7%** for PVSK/AlOx and **6.9%** for PVSK/LiF, directly improving voltage and fill factor (Source: nature.com).\n*   **Optical Losses:** Integrated reflection loss in all-perovskite tandem solar cells (APTSCs) amounts to **8.81 mA cm⁻²**. In 4-terminal configurations, significant optical losses arise from parasitic absorption by three electrodes and increased reflections from additional interfaces, whereas 2-terminal configurations exhibit lower optical losses despite greater fabrication complexity (Source: nature.com).\n*   **Degradation-Induced Electrical Losses:** The recombination (tunnel) junction, typically made of indium tin oxide (ITO) or nanocrystalline silicon, suffers from increased series resistance due to the diffusion of ionic species from the perovskite layer and mechanical stress from mismatched thermal expansion coefficients. This degradation reduces current-matching efficiency and promotes delamination (Source: patsnap.com).\n*   **Light-Induced Ion Migration:** Light exposure generates extra ions that migrate and screen the built-in electric field, leading to charge accumulation near the hole-selective contact. This increases recombination at the HTL–perovskite interface, causing significant performance decreases (Source: mdpi.com).\n\nSources:\n*   https://www.nature.com/articles/s41467-025-64467-y\n*   https://www.nature.com/articles/s41377-025-02120-5\n*   https://www.patsnap.com/resources/blog/articles/perovskite-silicon-tandem-solar-cell-stability-barriers\n*   https://www.mdpi.com/2079-9292/14/22/4428"}</t>
+  </si>
+  <si>
+    <t>{"output":"Based on the provided context, specific performance benchmarks comparing Retrieval-Aware Fine-Tuning (RAFT) directly against standard RAG pipelines are limited. The sources indicate that RAFT achieves an **86.3% accuracy rate** in product classification, but the text explicitly notes that RAG and Fine-Tuning (FT) values are \"not completely comparable across different tasks\" and are listed only as estimated values. (Source: link.springer.com/article/10.1007/s44443-025-00334-6)\n\nWhile direct numerical comparisons between RAFT and RAG are absent, the context provides the following related performance metrics and qualitative distinctions:\n\n*   **RAFT vs. RAG/FT Qualitative Comparison:** RAG reduces hallucinations through external evidence but is susceptible to retrieval noise. RAFT is noted to enhance adaptability to noisy or fuzzy inputs, whereas standard Fine-Tuning (FT) is more constrained by static knowledge limitations. (Source: link.springer.com/article/10.1007/s44443-025-00334-6)\n*   **RAG Pipeline Benchmarks (General):** In a separate evaluation of RAG pipelines using the Deepchecks framework, specific F1 scores were not provided for the RAG system itself, but the evaluation focused on retrieval relevance, contextual grounding, completeness, and safety. (Source: arxiv.org/html/2605.14488v1)\n*   **Advanced Retrieval Architectures:** Hierarchical retrieval pipelines (e.g., the CPS framework) achieved **ROUGE-2 F1 = 0.558** and **ROUGE-SU4 F1 = 0.573** on ideal answer generation in biomedical QA. Multimodal hybrid systems with domain-aware retrieval improved factual accuracy by **18.5%** in medical visual QA and **69.1%** in report generation. (Source: pmc.ncbi.nlm.nih.gov/articles/PMC12938813)\n*   **Human-AI Agreement:** In studies involving RAG mechanisms, Cohen’s Kappa for human-AI agreement ranged from **0.69 to 0.65**, and F1 scores were **0.85** for prediction and **0.83** for explanation. (Source: link.springer.com/article/10.1007/s44443-025-00334-6)\n\n**Truth Gap Flag:** The retrieved sources do not contain a direct, like-for-like numerical comparison (e.g., RAFT F1 vs. RAG F1) for the same specific task. The 86.3% accuracy for RAFT is isolated to product classification, and the RAG metrics provided are from different contexts (biomedical QA, general RAG evaluation) or are qualitative.\n\nSources:\n*   https://arxiv.org/html/2605.14488v1\n*   https://link.springer.com/article/10.1007/s44443-025-00334-6\n*   https://pmc.ncbi.nlm.nih.gov/articles/PMC12938813"}</t>
+  </si>
+  <si>
+    <t>{"output":"Recent modifications to the RoPE mechanism to extend context lengths primarily involve frequency-aware interpolation and attention scaling. The most prominent technique, **YaRN (Yet another RoPE extensioN method)**, groups RoPE dimensions into low, high, and intermediate frequencies, applying different interpolation strategies to each group and introducing a temperature scaling factor to attention logits to prevent perplexity degradation. (Source: daily.dev/posts/extending-the-rope-jonzmt2tf, github.com/xiaguan/pegainfer/issues/8)\n\nSpecific technical modifications include:\n\n*   **YaRN (Piecewise Scaling):** This method keeps high-frequency dimensions (small λ) unchanged to preserve local positional discrimination, applies linear interpolation to low-frequency dimensions (large λ), and uses a smooth ramp for mid-frequency dimensions. It also incorporates an attention temperature scaling factor to maintain the magnitude of attention scores at long contexts. (Source: localaimaster.com/blog/rope-yarn-long-context-guide)\n*   **NTK-Aware Scaling:** This approach modifies the RoPE base using the formula `new_base = base scale^(D / (D-2))`, where `scale` is the context extension factor and `D` is the head dimension. This preserves high-frequency dimensions while stretching low-frequency ones, though quality drops noticeably for extensions of **8x** or more. (Source: localaimaster.com/blog/rope-yarn-long-context-guide)\n*   **LongRoPE:** This technique proposes frequency reparameterization of RoPE embeddings to improve long-context extrapolation by stretching or compressing rotary frequencies across positions. Unlike YaRN, which is manually designed, LongRoPE is optimized end-to-end. (Source: arxiv.org/html/2602.10959v1)\n*   **Position Interpolation (PI) and Dynamic Scaling:** These are earlier techniques that involve scaling the position indices or dynamically adjusting the scaling factor, though they generally underperform compared to YaRN in terms of perplexity on extended contexts. (Source: daily.dev/posts/extending-the-rope-jonzmt2tf)\n\nSources:\n*   https://daily.dev/posts/extending-the-rope-jonzmt2tf\n*   https://github.com/xiaguan/pegainfer/issues/8\n*   https://arxiv.org/html/2602.10959v1\n*   https://localaimaster.com/blog/rope-yarn-long-context-guide\n*   https://www.linkedin.com/posts/aroraaman_most-modern-day-llms-such-as-qwen-deepseek-activity-7376191724932509696-22lh"}</t>
+  </si>
+  <si>
+    <t>{"output":"The provided context does not contain information regarding the specific mechanism of action or efficacy rates for the latest CRISPR-Cas12 or Cas13 variants utilized in recent gene-editing trials. While the text notes that Cas13 targets RNA and Cas9/Cas12 target DNA, it lacks specific clinical trial data, numerical efficacy rates, or details on recent variant mechanisms for these specific systems.\n\nKey points from the context:\n*   **Cas13 Mechanism:** Cas13 is an endonuclease that targets RNA (unlike Cas9/Cas12 which target DNA) by binding and cleaving specific single-stranded RNAs (ssRNAs) using a guide RNA. It performs two functions: processing its own crRNA and cleaving target RNA. (Source: pmc.ncbi.nlm.nih.gov)\n*   **Cas13 Efficacy:** One study mentioned achieved **&gt;25% correction** of a targeted stop codon in a mammalian cell culture model, but this is a preclinical result, not a clinical trial efficacy rate. (Source: pmc.ncbi.nlm.nih.gov)\n*   **Cas12/Cas9 Context:** The text states that clinical translation has been predominantly anchored in DNA editing via Cas9 and Cas12a, but it does not provide specific mechanisms or efficacy rates for recent Cas12 variants in trials. (Source: en.wikipedia.org)\n*   **General Trial Success:** The context mentions high success rates of **70%–95%** in advanced CRISPR trials generally, but does not attribute these specific percentages to Cas12 or Cas13 variants. (Source: sciencedirect.com)\n\nSources:\n*   https://pmc.ncbi.nlm.nih.gov/articles/PMC12506487\n*   https://en.wikipedia.org/wiki/CRISPR_gene_editing\n*   https://www.sciencedirect.com/science/article/pii/S2590262825000875"}</t>
   </si>
 </sst>
 </file>
@@ -236,16 +265,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,16 +558,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" customWidth="1"/>
     <col min="2" max="2" width="51.5546875" customWidth="1"/>
     <col min="3" max="3" width="38.5546875" customWidth="1"/>
     <col min="4" max="4" width="94.44140625" customWidth="1"/>
+    <col min="5" max="5" width="100.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -549,8 +581,11 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -560,8 +595,11 @@
       <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>7</v>
       </c>
@@ -571,8 +609,11 @@
       <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>10</v>
       </c>
@@ -582,19 +623,25 @@
       <c r="D4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -604,19 +651,25 @@
       <c r="D6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -626,19 +679,25 @@
       <c r="D8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>28</v>
       </c>
@@ -648,16 +707,22 @@
       <c r="D10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>32</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
